--- a/experiments/prompt-tuning/hc+ft/Results/CARDD_QWEN_temp_1/cardd_prompt03_r1.xlsx
+++ b/experiments/prompt-tuning/hc+ft/Results/CARDD_QWEN_temp_1/cardd_prompt03_r1.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UshariRanasinghe\Desktop\Projects\vlm-research\experiments\prompt-tuning\hc+ft\Results\CARDD_QWEN_temp_1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C734DA1-CFE6-4DA9-97F9-BA6F4AD7E054}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="20" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="evaluation" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -109,8 +115,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,6 +179,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -193,7 +207,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="image_1.png"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="image_1.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -231,7 +251,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="image_2.png"/>
+        <xdr:cNvPr id="3" name="Picture 2" descr="image_2.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -269,7 +295,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3" descr="image_3.png"/>
+        <xdr:cNvPr id="4" name="Picture 3" descr="image_3.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -307,7 +339,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4" descr="image_4.png"/>
+        <xdr:cNvPr id="5" name="Picture 4" descr="image_4.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -345,7 +383,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5" descr="image_5.png"/>
+        <xdr:cNvPr id="6" name="Picture 5" descr="image_5.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -383,7 +427,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6" descr="image_6.png"/>
+        <xdr:cNvPr id="7" name="Picture 6" descr="image_6.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -421,7 +471,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7" descr="image_7.png"/>
+        <xdr:cNvPr id="8" name="Picture 7" descr="image_7.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -459,7 +515,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8" descr="image_8.png"/>
+        <xdr:cNvPr id="9" name="Picture 8" descr="image_8.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -497,7 +559,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9" descr="image_9.png"/>
+        <xdr:cNvPr id="10" name="Picture 9" descr="image_9.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -535,7 +603,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10" descr="image_10.png"/>
+        <xdr:cNvPr id="11" name="Picture 10" descr="image_10.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -604,7 +678,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -636,9 +710,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -670,6 +762,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -845,11 +955,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="141.90625" customWidth="1"/>
+    <col min="5" max="5" width="166.54296875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="2:10">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -878,7 +992,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2">
         <v>0</v>
       </c>
@@ -892,22 +1006,22 @@
         <v>20</v>
       </c>
       <c r="F2">
-        <v>0.8162127733230591</v>
+        <v>0.81621277332305908</v>
       </c>
       <c r="G2">
         <v>0.2153846153846154</v>
       </c>
       <c r="H2">
-        <v>1.913938800449713</v>
+        <v>1.9139388004497131</v>
       </c>
       <c r="I2">
         <v>7133.96240234375</v>
       </c>
       <c r="J2">
-        <v>20.38595414161682</v>
+        <v>20.385954141616821</v>
       </c>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3">
         <v>1</v>
       </c>
@@ -921,10 +1035,10 @@
         <v>21</v>
       </c>
       <c r="F3">
-        <v>0.6698369383811951</v>
+        <v>0.66983693838119507</v>
       </c>
       <c r="G3">
-        <v>0.2857142857142858</v>
+        <v>0.28571428571428581</v>
       </c>
       <c r="H3">
         <v>2.014879765866465</v>
@@ -936,7 +1050,7 @@
         <v>6.364332914352417</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>2</v>
       </c>
@@ -950,10 +1064,10 @@
         <v>22</v>
       </c>
       <c r="F4">
-        <v>0.8263037204742432</v>
+        <v>0.82630372047424316</v>
       </c>
       <c r="G4">
-        <v>0.1971830985915493</v>
+        <v>0.19718309859154931</v>
       </c>
       <c r="H4">
         <v>2.209307138774868</v>
@@ -962,10 +1076,10 @@
         <v>7118.92578125</v>
       </c>
       <c r="J4">
-        <v>5.424737215042114</v>
+        <v>5.4247372150421143</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>3</v>
       </c>
@@ -979,7 +1093,7 @@
         <v>23</v>
       </c>
       <c r="F5">
-        <v>0.7745883464813232</v>
+        <v>0.77458834648132324</v>
       </c>
       <c r="G5">
         <v>0.1388888888888889</v>
@@ -991,10 +1105,10 @@
         <v>7118.92578125</v>
       </c>
       <c r="J5">
-        <v>5.633186101913452</v>
+        <v>5.6331861019134521</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>4</v>
       </c>
@@ -1008,22 +1122,22 @@
         <v>24</v>
       </c>
       <c r="F6">
-        <v>0.8654950857162476</v>
+        <v>0.86549508571624756</v>
       </c>
       <c r="G6">
         <v>0.21875</v>
       </c>
       <c r="H6">
-        <v>2.326957039043929</v>
+        <v>2.3269570390439291</v>
       </c>
       <c r="I6">
         <v>7118.92578125</v>
       </c>
       <c r="J6">
-        <v>6.196205615997314</v>
+        <v>6.1962056159973136</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>5</v>
       </c>
@@ -1037,13 +1151,13 @@
         <v>25</v>
       </c>
       <c r="F7">
-        <v>0.7168500423431396</v>
+        <v>0.71685004234313965</v>
       </c>
       <c r="G7">
         <v>0.2105263157894737</v>
       </c>
       <c r="H7">
-        <v>2.083438823960231</v>
+        <v>2.0834388239602308</v>
       </c>
       <c r="I7">
         <v>7118.92578125</v>
@@ -1052,7 +1166,7 @@
         <v>6.858677864074707</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>6</v>
       </c>
@@ -1066,10 +1180,10 @@
         <v>26</v>
       </c>
       <c r="F8">
-        <v>0.5887110233306885</v>
+        <v>0.58871102333068848</v>
       </c>
       <c r="G8">
-        <v>0.225</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="H8">
         <v>1.418792325533295</v>
@@ -1078,10 +1192,10 @@
         <v>7118.92578125</v>
       </c>
       <c r="J8">
-        <v>9.66773533821106</v>
+        <v>9.6677353382110596</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>7</v>
       </c>
@@ -1095,22 +1209,22 @@
         <v>27</v>
       </c>
       <c r="F9">
-        <v>0.8131297826766968</v>
+        <v>0.81312978267669678</v>
       </c>
       <c r="G9">
-        <v>0.3137254901960784</v>
+        <v>0.31372549019607843</v>
       </c>
       <c r="H9">
-        <v>2.838622296872477</v>
+        <v>2.8386222968724768</v>
       </c>
       <c r="I9">
         <v>7118.92578125</v>
       </c>
       <c r="J9">
-        <v>9.378527402877808</v>
+        <v>9.3785274028778076</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>8</v>
       </c>
@@ -1124,10 +1238,10 @@
         <v>28</v>
       </c>
       <c r="F10">
-        <v>0.6820347309112549</v>
+        <v>0.68203473091125488</v>
       </c>
       <c r="G10">
-        <v>0.2439024390243902</v>
+        <v>0.24390243902439021</v>
       </c>
       <c r="H10">
         <v>1.441059436997856</v>
@@ -1136,10 +1250,10 @@
         <v>7118.92578125</v>
       </c>
       <c r="J10">
-        <v>6.600096464157104</v>
+        <v>6.6000964641571036</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>9</v>
       </c>
@@ -1156,10 +1270,10 @@
         <v>0.704215407371521</v>
       </c>
       <c r="G11">
-        <v>0.1643835616438356</v>
+        <v>0.16438356164383561</v>
       </c>
       <c r="H11">
-        <v>2.115606349567548</v>
+        <v>2.1156063495675479</v>
       </c>
       <c r="I11">
         <v>7118.92578125</v>
